--- a/output/pdf_financials_xlsx/MGRO.xlsx
+++ b/output/pdf_financials_xlsx/MGRO.xlsx
@@ -939,10 +939,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.003322</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.103547</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
@@ -1693,10 +1693,10 @@
         <v>-1.518038</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-3.063875</v>
+        <v>-3.067197</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-5.565841</v>
+        <v>-5.669388</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -1789,10 +1789,10 @@
         <v>-1.518038</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-3.063875</v>
+        <v>-3.067197</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-5.565841</v>
+        <v>-5.669388</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-23808.18245395913</v>
+        <v>-23833.99642551869</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-85905.86510263929</v>
+        <v>-87504.05926840562</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -1984,13 +1984,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.003504</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000937</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.007156</v>
@@ -2064,13 +2064,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.003504</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000937</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.007156</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
